--- a/class test/class test 7/test record class 7 c 2026.xlsx
+++ b/class test/class test 7/test record class 7 c 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{053DBCB7-8555-4465-B039-87242CD128C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4091947-7458-4E2C-ABF6-1FB05DABD592}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{053DBCB7-8555-4465-B039-87242CD128C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89C50C33-41B7-4195-95EA-FD1413A78096}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="96">
   <si>
     <t>SESSION 2026-27</t>
   </si>
@@ -321,6 +321,12 @@
   </si>
   <si>
     <t>ch 4</t>
+  </si>
+  <si>
+    <t>ch5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MM 11</t>
   </si>
 </sst>
 </file>
@@ -424,7 +430,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -447,57 +453,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -533,27 +493,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -650,6 +601,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -969,7 +924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.453125" customWidth="1"/>
@@ -979,27 +934,29 @@
     <col min="5" max="5" width="11.26953125" customWidth="1"/>
     <col min="6" max="6" width="11.26953125" hidden="1" customWidth="1"/>
     <col min="7" max="8" width="11.26953125" customWidth="1"/>
-    <col min="9" max="1025" width="8.1796875" customWidth="1"/>
+    <col min="9" max="9" width="8.26953125" customWidth="1"/>
+    <col min="10" max="1026" width="8.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-    </row>
-    <row r="2" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="15" t="s">
+    <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+    </row>
+    <row r="2" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="12" t="s">
         <v>89</v>
       </c>
@@ -1014,34 +971,40 @@
       <c r="H2" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="12" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+      <c r="J2" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="14">
+      <c r="B3" s="15"/>
+      <c r="C3" s="16">
         <v>46114</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14">
+      <c r="D3" s="16"/>
+      <c r="E3" s="16">
         <v>46136</v>
       </c>
-      <c r="F3" s="14"/>
+      <c r="F3" s="16"/>
       <c r="G3" s="1">
         <v>46150</v>
       </c>
       <c r="H3" s="2">
         <v>46185</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="13">
         <v>46227</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J3" s="13">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1069,8 +1032,11 @@
       <c r="I4" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J4" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1097,11 +1063,14 @@
       <c r="H5" s="8">
         <v>4</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="14" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J5" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
@@ -1128,11 +1097,14 @@
       <c r="H6" s="8">
         <v>0</v>
       </c>
-      <c r="I6" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I6" s="14">
+        <v>0</v>
+      </c>
+      <c r="J6" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
@@ -1159,11 +1131,14 @@
       <c r="H7" s="8">
         <v>7</v>
       </c>
-      <c r="I7" s="19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I7" s="14">
+        <v>6</v>
+      </c>
+      <c r="J7" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
@@ -1190,11 +1165,14 @@
       <c r="H8" s="8">
         <v>1</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="14">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J8" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
         <v>16</v>
       </c>
@@ -1221,11 +1199,14 @@
       <c r="H9" s="8">
         <v>8</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="14">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J9" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
@@ -1252,11 +1233,14 @@
       <c r="H10" s="8">
         <v>3</v>
       </c>
-      <c r="I10" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I10" s="14">
+        <v>0</v>
+      </c>
+      <c r="J10" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
@@ -1283,11 +1267,14 @@
       <c r="H11" s="8">
         <v>2</v>
       </c>
-      <c r="I11" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I11" s="14">
+        <v>0</v>
+      </c>
+      <c r="J11" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
         <v>22</v>
       </c>
@@ -1314,11 +1301,14 @@
       <c r="H12" s="8">
         <v>5</v>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J12" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
         <v>24</v>
       </c>
@@ -1345,11 +1335,14 @@
       <c r="H13" s="8">
         <v>3</v>
       </c>
-      <c r="I13" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I13" s="14">
+        <v>0</v>
+      </c>
+      <c r="J13" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
         <v>26</v>
       </c>
@@ -1376,11 +1369,14 @@
       <c r="H14" s="8">
         <v>8</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="I14" s="14" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J14" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
@@ -1404,11 +1400,14 @@
       <c r="H15" s="8">
         <v>2</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J15" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A16" s="5" t="s">
         <v>30</v>
       </c>
@@ -1432,11 +1431,14 @@
       <c r="H16" s="8">
         <v>3</v>
       </c>
-      <c r="I16" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I16" s="14">
+        <v>0</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A17" s="5" t="s">
         <v>32</v>
       </c>
@@ -1463,11 +1465,14 @@
       <c r="H17" s="8">
         <v>4</v>
       </c>
-      <c r="I17" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I17" s="14">
+        <v>0</v>
+      </c>
+      <c r="J17" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A18" s="5" t="s">
         <v>34</v>
       </c>
@@ -1494,11 +1499,14 @@
       <c r="H18" s="8">
         <v>6</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J18" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A19" s="5" t="s">
         <v>36</v>
       </c>
@@ -1522,11 +1530,14 @@
       <c r="H19" s="8">
         <v>6</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J19" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
@@ -1553,11 +1564,14 @@
       <c r="H20" s="8">
         <v>3</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J20" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
@@ -1584,11 +1598,14 @@
       <c r="H21" s="8">
         <v>10</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J21" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A22" s="5" t="s">
         <v>42</v>
       </c>
@@ -1615,11 +1632,14 @@
       <c r="H22" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J22" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A23" s="5" t="s">
         <v>44</v>
       </c>
@@ -1646,11 +1666,14 @@
       <c r="H23" s="8">
         <v>5</v>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="14">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J23" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A24" s="5" t="s">
         <v>46</v>
       </c>
@@ -1674,11 +1697,14 @@
       <c r="H24" s="8">
         <v>7</v>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J24" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A25" s="5" t="s">
         <v>48</v>
       </c>
@@ -1702,11 +1728,14 @@
       <c r="H25" s="8">
         <v>8</v>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J25" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A26" s="5" t="s">
         <v>50</v>
       </c>
@@ -1730,11 +1759,14 @@
       <c r="H26" s="8">
         <v>7.5</v>
       </c>
-      <c r="I26" s="19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I26" s="14">
+        <v>6</v>
+      </c>
+      <c r="J26" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A27" s="5" t="s">
         <v>52</v>
       </c>
@@ -1761,11 +1793,14 @@
       <c r="H27" s="8">
         <v>10</v>
       </c>
-      <c r="I27" s="19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I27" s="14">
+        <v>6</v>
+      </c>
+      <c r="J27" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A28" s="5" t="s">
         <v>54</v>
       </c>
@@ -1792,11 +1827,14 @@
       <c r="H28" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J28" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A29" s="5" t="s">
         <v>56</v>
       </c>
@@ -1823,11 +1861,14 @@
       <c r="H29" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="I29" s="19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I29" s="14">
+        <v>6</v>
+      </c>
+      <c r="J29" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A30" s="5" t="s">
         <v>58</v>
       </c>
@@ -1854,11 +1895,14 @@
       <c r="H30" s="8">
         <v>7.5</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="14">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J30" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A31" s="5" t="s">
         <v>60</v>
       </c>
@@ -1885,11 +1929,14 @@
       <c r="H31" s="8">
         <v>7</v>
       </c>
-      <c r="I31" s="19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I31" s="14">
+        <v>6</v>
+      </c>
+      <c r="J31" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A32" s="5" t="s">
         <v>62</v>
       </c>
@@ -1916,11 +1963,14 @@
       <c r="H32" s="8">
         <v>5</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="14">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J32" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A33" s="5" t="s">
         <v>64</v>
       </c>
@@ -1947,11 +1997,14 @@
       <c r="H33" s="8">
         <v>4</v>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J33" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A34" s="5" t="s">
         <v>66</v>
       </c>
@@ -1978,11 +2031,14 @@
       <c r="H34" s="8">
         <v>4</v>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J34" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A35" s="5" t="s">
         <v>68</v>
       </c>
@@ -2009,11 +2065,14 @@
       <c r="H35" s="8">
         <v>9</v>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J35" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A36" s="5" t="s">
         <v>70</v>
       </c>
@@ -2040,11 +2099,14 @@
       <c r="H36" s="8">
         <v>6</v>
       </c>
-      <c r="I36" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I36" s="14">
+        <v>0</v>
+      </c>
+      <c r="J36" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A37" s="5" t="s">
         <v>72</v>
       </c>
@@ -2071,11 +2133,14 @@
       <c r="H37" s="8">
         <v>7</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J37" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A38" s="5" t="s">
         <v>74</v>
       </c>
@@ -2102,11 +2167,14 @@
       <c r="H38" s="8">
         <v>0</v>
       </c>
-      <c r="I38" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I38" s="14">
+        <v>0</v>
+      </c>
+      <c r="J38" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A39" s="5" t="s">
         <v>76</v>
       </c>
@@ -2133,11 +2201,14 @@
       <c r="H39" s="8">
         <v>1</v>
       </c>
-      <c r="I39" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="I39" s="14">
+        <v>0</v>
+      </c>
+      <c r="J39" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A40" s="5" t="s">
         <v>77</v>
       </c>
@@ -2164,11 +2235,14 @@
       <c r="H40" s="8">
         <v>1</v>
       </c>
-      <c r="I40" s="19">
+      <c r="I40" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J40" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A41" s="5" t="s">
         <v>79</v>
       </c>
@@ -2192,11 +2266,14 @@
       <c r="H41" s="8">
         <v>3</v>
       </c>
-      <c r="I41" s="19">
+      <c r="I41" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J41" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A42" s="5" t="s">
         <v>81</v>
       </c>
@@ -2220,11 +2297,14 @@
       <c r="H42" s="8">
         <v>7</v>
       </c>
-      <c r="I42" s="19">
+      <c r="I42" s="14">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J42" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A43" s="5" t="s">
         <v>83</v>
       </c>
@@ -2245,11 +2325,14 @@
       <c r="H43" s="8">
         <v>10</v>
       </c>
-      <c r="I43" s="19">
+      <c r="I43" s="14">
         <v>7</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="J43" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A44" s="5" t="s">
         <v>85</v>
       </c>
@@ -2270,7 +2353,10 @@
       <c r="H44" s="8">
         <v>6</v>
       </c>
-      <c r="I44" s="19">
+      <c r="I44" s="14">
+        <v>8</v>
+      </c>
+      <c r="J44" s="14">
         <v>8</v>
       </c>
     </row>
@@ -2280,7 +2366,7 @@
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="D5:D44 F5:F44">

--- a/class test/class test 7/test record class 7 c 2026.xlsx
+++ b/class test/class test 7/test record class 7 c 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{053DBCB7-8555-4465-B039-87242CD128C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89C50C33-41B7-4195-95EA-FD1413A78096}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="13_ncr:1_{053DBCB7-8555-4465-B039-87242CD128C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{765168CF-C45E-42C3-AACF-69D20D952B05}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="96">
   <si>
     <t>SESSION 2026-27</t>
   </si>
@@ -326,7 +326,7 @@
     <t>ch5</t>
   </si>
   <si>
-    <t xml:space="preserve"> MM 11</t>
+    <t>ch6</t>
   </si>
 </sst>
 </file>
@@ -457,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -502,9 +502,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -924,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.453125" customWidth="1"/>
@@ -938,7 +935,7 @@
     <col min="10" max="1026" width="8.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -952,7 +949,7 @@
       <c r="I1" s="17"/>
       <c r="J1" s="17"/>
     </row>
-    <row r="2" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A2" s="17" t="s">
         <v>92</v>
       </c>
@@ -974,11 +971,14 @@
       <c r="I2" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="12" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K2" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
@@ -1003,8 +1003,11 @@
       <c r="J3" s="13">
         <v>46238</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="K3" s="13">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1033,10 +1036,13 @@
         <v>6</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1069,8 +1075,11 @@
       <c r="J5" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K5" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
@@ -1103,8 +1112,11 @@
       <c r="J6" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K6" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
@@ -1137,8 +1149,11 @@
       <c r="J7" s="14">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K7" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
@@ -1171,8 +1186,11 @@
       <c r="J8" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K8" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
         <v>16</v>
       </c>
@@ -1205,8 +1223,11 @@
       <c r="J9" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K9" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
@@ -1239,8 +1260,11 @@
       <c r="J10" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K10" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
@@ -1273,8 +1297,11 @@
       <c r="J11" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K11" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
         <v>22</v>
       </c>
@@ -1307,8 +1334,11 @@
       <c r="J12" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K12" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
         <v>24</v>
       </c>
@@ -1341,8 +1371,11 @@
       <c r="J13" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K13" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
         <v>26</v>
       </c>
@@ -1375,8 +1408,11 @@
       <c r="J14" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K14" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
@@ -1406,8 +1442,11 @@
       <c r="J15" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K15" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A16" s="5" t="s">
         <v>30</v>
       </c>
@@ -1437,8 +1476,11 @@
       <c r="J16" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K16" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A17" s="5" t="s">
         <v>32</v>
       </c>
@@ -1471,8 +1513,11 @@
       <c r="J17" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K17" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A18" s="5" t="s">
         <v>34</v>
       </c>
@@ -1505,8 +1550,11 @@
       <c r="J18" s="14">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K18" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A19" s="5" t="s">
         <v>36</v>
       </c>
@@ -1536,8 +1584,11 @@
       <c r="J19" s="14">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K19" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
@@ -1570,8 +1621,11 @@
       <c r="J20" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K20" s="14">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
@@ -1604,8 +1658,11 @@
       <c r="J21" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K21" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A22" s="5" t="s">
         <v>42</v>
       </c>
@@ -1638,8 +1695,11 @@
       <c r="J22" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K22" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A23" s="5" t="s">
         <v>44</v>
       </c>
@@ -1672,8 +1732,11 @@
       <c r="J23" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K23" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A24" s="5" t="s">
         <v>46</v>
       </c>
@@ -1703,8 +1766,11 @@
       <c r="J24" s="14">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K24" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A25" s="5" t="s">
         <v>48</v>
       </c>
@@ -1734,8 +1800,11 @@
       <c r="J25" s="14">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K25" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A26" s="5" t="s">
         <v>50</v>
       </c>
@@ -1765,8 +1834,11 @@
       <c r="J26" s="14">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K26" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A27" s="5" t="s">
         <v>52</v>
       </c>
@@ -1799,8 +1871,11 @@
       <c r="J27" s="14">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K27" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A28" s="5" t="s">
         <v>54</v>
       </c>
@@ -1833,8 +1908,11 @@
       <c r="J28" s="14">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K28" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A29" s="5" t="s">
         <v>56</v>
       </c>
@@ -1867,8 +1945,11 @@
       <c r="J29" s="14">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K29" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A30" s="5" t="s">
         <v>58</v>
       </c>
@@ -1901,8 +1982,11 @@
       <c r="J30" s="14">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K30" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A31" s="5" t="s">
         <v>60</v>
       </c>
@@ -1935,8 +2019,11 @@
       <c r="J31" s="14">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K31" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A32" s="5" t="s">
         <v>62</v>
       </c>
@@ -1969,8 +2056,11 @@
       <c r="J32" s="14">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K32" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A33" s="5" t="s">
         <v>64</v>
       </c>
@@ -2003,8 +2093,11 @@
       <c r="J33" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K33" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A34" s="5" t="s">
         <v>66</v>
       </c>
@@ -2037,8 +2130,11 @@
       <c r="J34" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K34" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A35" s="5" t="s">
         <v>68</v>
       </c>
@@ -2071,8 +2167,11 @@
       <c r="J35" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K35" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A36" s="5" t="s">
         <v>70</v>
       </c>
@@ -2105,8 +2204,11 @@
       <c r="J36" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K36" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A37" s="5" t="s">
         <v>72</v>
       </c>
@@ -2139,8 +2241,11 @@
       <c r="J37" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K37" s="14">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A38" s="5" t="s">
         <v>74</v>
       </c>
@@ -2173,8 +2278,11 @@
       <c r="J38" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K38" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A39" s="5" t="s">
         <v>76</v>
       </c>
@@ -2207,8 +2315,11 @@
       <c r="J39" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K39" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A40" s="5" t="s">
         <v>77</v>
       </c>
@@ -2241,8 +2352,11 @@
       <c r="J40" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K40" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A41" s="5" t="s">
         <v>79</v>
       </c>
@@ -2272,8 +2386,11 @@
       <c r="J41" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K41" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A42" s="5" t="s">
         <v>81</v>
       </c>
@@ -2303,8 +2420,11 @@
       <c r="J42" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K42" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A43" s="5" t="s">
         <v>83</v>
       </c>
@@ -2331,8 +2451,11 @@
       <c r="J43" s="14">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K43" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A44" s="5" t="s">
         <v>85</v>
       </c>
@@ -2358,6 +2481,9 @@
       </c>
       <c r="J44" s="14">
         <v>8</v>
+      </c>
+      <c r="K44" s="14">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/class test/class test 7/test record class 7 c 2026.xlsx
+++ b/class test/class test 7/test record class 7 c 2026.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="13_ncr:1_{053DBCB7-8555-4465-B039-87242CD128C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{765168CF-C45E-42C3-AACF-69D20D952B05}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="13_ncr:1_{053DBCB7-8555-4465-B039-87242CD128C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E77DC6A-C61B-4E5F-86B8-C3AF89C56F32}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="CT" sheetId="1" r:id="rId1"/>
+    <sheet name="PT" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet1!$A$4:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">CT!$A$4:$D$4</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="139">
   <si>
     <t>SESSION 2026-27</t>
   </si>
@@ -327,13 +328,142 @@
   </si>
   <si>
     <t>ch6</t>
+  </si>
+  <si>
+    <t>SUBJECT</t>
+  </si>
+  <si>
+    <t>MATHS</t>
+  </si>
+  <si>
+    <t>MM</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABHAY KUMAR </t>
+  </si>
+  <si>
+    <t>ABHINAY</t>
+  </si>
+  <si>
+    <t>ANAIKA</t>
+  </si>
+  <si>
+    <t>ARYAN</t>
+  </si>
+  <si>
+    <t>BHAVIKA</t>
+  </si>
+  <si>
+    <t>CHANDNI</t>
+  </si>
+  <si>
+    <t>DIPIKA</t>
+  </si>
+  <si>
+    <t>DISHA</t>
+  </si>
+  <si>
+    <t>GEETA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUNJAN </t>
+  </si>
+  <si>
+    <t>HARSHUL</t>
+  </si>
+  <si>
+    <t>HIMANSHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAMAL SINGH </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KARTIK </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KARTIKA GODIYAL </t>
+  </si>
+  <si>
+    <t>KARTIKA RAWAT</t>
+  </si>
+  <si>
+    <t>KARISHMA</t>
+  </si>
+  <si>
+    <t>LAKSHIT rawat</t>
+  </si>
+  <si>
+    <t>LAKSHIT SINGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALVIKA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOULIK </t>
+  </si>
+  <si>
+    <t>MOITRIKA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRITYUNJAY CHANDRA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUNKASHIF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAITIK </t>
+  </si>
+  <si>
+    <t>NAMAN SATI</t>
+  </si>
+  <si>
+    <t>NAMAN TAMTA</t>
+  </si>
+  <si>
+    <t>NISHTHI</t>
+  </si>
+  <si>
+    <t>PARIDHI</t>
+  </si>
+  <si>
+    <t>PARTH</t>
+  </si>
+  <si>
+    <t>PRACHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRASHUN </t>
+  </si>
+  <si>
+    <t>RUDRAPRATAP</t>
+  </si>
+  <si>
+    <t>SHRAVANI</t>
+  </si>
+  <si>
+    <t>TANISHA</t>
+  </si>
+  <si>
+    <t>YAMAN</t>
+  </si>
+  <si>
+    <t>YASHPAL</t>
+  </si>
+  <si>
+    <t>ARPITA</t>
+  </si>
+  <si>
+    <t>MAANSHA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -421,6 +551,22 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -430,7 +576,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -453,11 +599,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -504,6 +708,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2503,4 +2726,364 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E89F8BA-AA24-4F3A-8290-E30B5D2C5940}">
+  <dimension ref="A1:B45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="19">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="21"/>
+    </row>
+    <row r="4" spans="1:2" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" s="25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27" s="25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" s="25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" s="25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B37" s="25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" s="19">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" s="19">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B41" s="19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42" s="19">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" s="19">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="26"/>
+      <c r="B44" s="26"/>
+    </row>
+    <row r="45" spans="1:2" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>